--- a/main/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/main/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:39:02+00:00</t>
+    <t>2026-07-07T07:06:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/main/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T07:06:09+00:00</t>
+    <t>2026-10-07T08:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/main/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T08:13:15+00:00</t>
+    <t>2026-10-07T08:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/main/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T08:21:30+00:00</t>
+    <t>2026-10-07T08:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/main/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T08:35:11+00:00</t>
+    <t>2026-10-07T09:00:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
